--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_la araucania.xlsx
@@ -87,12 +87,12 @@
     <t xml:space="preserve">Pucón</t>
   </si>
   <si>
+    <t xml:space="preserve">Lonquimay</t>
+  </si>
+  <si>
     <t xml:space="preserve">Purén</t>
   </si>
   <si>
-    <t xml:space="preserve">Lonquimay</t>
-  </si>
-  <si>
     <t xml:space="preserve">Curarrehue</t>
   </si>
   <si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:21</t>
+    <t xml:space="preserve">2026-09-09 23:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -860,7 +860,7 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>9208</v>
+        <v>9205</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2021</v>
@@ -877,7 +877,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>9205</v>
+        <v>9208</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2021</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:17</t>
+    <t xml:space="preserve">2026-09-17 14:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:13</t>
+    <t xml:space="preserve">2026-09-23 12:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:41</t>
+    <t xml:space="preserve">2026-10-02 14:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:58</t>
+    <t xml:space="preserve">2026-10-05 11:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
